--- a/publishing/accessibility/springer_alt_text_inventory.xlsx
+++ b/publishing/accessibility/springer_alt_text_inventory.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb04ac95ae93d45ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="Rcd12e96bd9cb48ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R5602e3a4d5d24e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb04d350eb2c34cac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R0e158dcf390642db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R78512e494ce34d44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -323,7 +323,7 @@
         <x:v>Generated at UTC</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>46191.06027412037</x:v>
+        <x:v>46191.10914256945</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/publishing/accessibility/springer_alt_text_inventory.xlsx
+++ b/publishing/accessibility/springer_alt_text_inventory.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0f290d3c2043460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R0e6d76ccec04478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R0adf59027e374c1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R96cc8c0e27bf4285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="Rcb1eac0eb3044b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R0a18deb6ffb14752"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -323,7 +323,7 @@
         <x:v>Generated at UTC</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>46192.32035923611</x:v>
+        <x:v>46195.21366738426</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1025,7 +1025,7 @@
         <x:v>front_matter_guide-1</x:v>
       </x:c>
       <x:c r="I2" s="4" t="str">
-        <x:v>Book architecture. Source: original illustration by the authors. The figure organizes the fourteen parts, forty-eight chapters, fifteen projects, and eight appendices around the data lifecycle, with layers for foundations, collection and processing, cross-cutting capabilities, model alignment, application governance, security and compliance, specialized practice, and project delivery; Alt text: book architecture diagram showing the data lifecycle, layered manuscript structure, DataOps flywheel, platform support capabilities, and engineering principles that run through the book. The book's core contributions appear in four areas</x:v>
+        <x:v>Book architecture. Source: original illustration by the authors. The figure organizes the fourteen parts, forty-eight chapters, fifteen projects, and eight appendices around the data lifecycle, with layers for foundations, collection and processing, cross-cutting capabilities, model alignment, application governance, security and compliance, specialized practice, and project delivery. The book's core contributions appear in four areas</x:v>
       </x:c>
       <x:c r="J2" s="4" t="str">
         <x:v>Book architecture of Data Engineering for Large Foundation Models, showing the data lifecycle, foundation layer, data collection and processing layer, cross-cutting capabilities, model alignment and capability enhancement layer, application governance layer, security and specialized practice layer, project case layer, DataOps flywheel, and platform support capabilities</x:v>
@@ -1043,7 +1043,7 @@
         <x:v>png</x:v>
       </x:c>
       <x:c r="O2" s="4" t="str">
-        <x:v>book architecture diagram showing the data lifecycle, layered manuscript structure, DataOps flywheel, platform support capabilities, and engineering principles that run through the book. The book's core contributions appear in four areas.</x:v>
+        <x:v>Book architecture. Source: original illustration by the authors. The figure organizes the fourteen parts, forty-eight chapters, fifteen projects, and eight appendices around the data lifecycle, with layers for foundations, collection and processing, cross-cutting capabilities, model alignment, application governance, security and compliance, specialized practice, and project delivery. The book's core contributions appear in four areas.</x:v>
       </x:c>
       <x:c r="P2" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Front Matter Guide; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -1057,7 +1057,7 @@
       <x:c r="S2" s="4" t="str"/>
       <x:c r="T2" s="4" t="str"/>
       <x:c r="U2" s="4" t="str">
-        <x:v>全书架构图。来源：本书自绘。该图以数据全生命周期为主线，将十四篇、四十八章、十五个项目和八个附录组织为基础、采集处理、横切能力、模型对齐、应用治理、安全合规、专项实践和项目交付等层级；Alt text：《大模型数据工程》全书架构图，展示数据全生命周期、主体篇章分层、DataOps 飞轮、平台支撑能力和贯穿全书的工程原则。 本书的核心贡献体现在四个方面</x:v>
+        <x:v>全书架构图。来源：本书自绘。该图以数据全生命周期为主线，将十四篇、四十八章、十五个项目和八个附录组织为基础、采集处理、横切能力、模型对齐、应用治理、安全合规、专项实践和项目交付等层级。 本书的核心贡献体现在四个方面</x:v>
       </x:c>
       <x:c r="V2" s="4" t="str">
         <x:v>《大模型数据工程》全书架构图，展示数据全生命周期、基础层、数据采集与处理层、横切能力、模型对齐与能力增强层、应用治理层、安全合规与专项实践层、项目实战层、DataOps 飞轮和平台支撑能力之间的关系</x:v>
@@ -1089,7 +1089,7 @@
         <x:v>1-1</x:v>
       </x:c>
       <x:c r="I3" s="4" t="str">
-        <x:v>Figure 1-1: LLM-Era Data Engineering Role Restructuring Diagram. Source: original illustration. The figure depicts the role flywheel loop spanning platform architecture, data collection, model fine-tuning and validation, and product-research iteration; Alt text: LLM-era data engineering role restructuring diagram showing the closed-loop interfaces among platform, data, algorithms, annotation, product, and compliance roles</x:v>
+        <x:v>Figure 1-1: LLM-Era Data Engineering Role Restructuring Diagram. Source: original illustration. The figure depicts the role flywheel loop spanning platform architecture, data collection, model fine-tuning and validation, and product-research iteration</x:v>
       </x:c>
       <x:c r="J3" s="4" t="str">
         <x:v>Figure 1-1: LLM-Era Data Engineering Role Restructuring Diagram, showing the closed-loop interfaces among platform, data, algorithms, annotation, product, and compliance roles</x:v>
@@ -1107,9 +1107,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O3" s="4" t="str">
-        <x:v>LLM-era data engineering role restructuring diagram showing the closed-loop interfaces among platform, data, algorithms, annotation, product, and compliance roles.</x:v>
-      </x:c>
-      <x:c r="P3" s="4" t="str"/>
+        <x:v>LLM-Era Data Engineering Role Restructuring Diagram. Source: original illustration. The figure depicts the role flywheel loop spanning platform architecture, data collection, model fine-tuning and validation, and product-research iteration.</x:v>
+      </x:c>
+      <x:c r="P3" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 1: The Data Revolution in the Era of Large Models; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q3" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -1119,7 +1121,7 @@
       <x:c r="S3" s="4" t="str"/>
       <x:c r="T3" s="4" t="str"/>
       <x:c r="U3" s="4" t="str">
-        <x:v>图1-1：大模型时代数据工程职责重构图。来源：本书自绘。该图展现了从平台架构、数据采集到模型微调验证再到产研迭代的角色飞轮闭环；Alt text：大模型时代数据工程职责重构图，展示平台、数据、算法、标注、产品与合规角色之间的闭环接口</x:v>
+        <x:v>图1-1：大模型时代数据工程职责重构图。来源：本书自绘。该图展现了从平台架构、数据采集到模型微调验证再到产研迭代的角色飞轮闭环</x:v>
       </x:c>
       <x:c r="V3" s="4" t="str">
         <x:v>图1-1：大模型时代数据工程职责重构图，展示平台、数据、算法、标注、产品与合规角色之间的闭环接口</x:v>
@@ -1151,7 +1153,7 @@
         <x:v>1-2</x:v>
       </x:c>
       <x:c r="I4" s="4" t="str">
-        <x:v>Figure 1-2: Full Fourteen-Part Lifecycle Map. Source: original illustration. The figure uses infrastructure as its foundation, threading through pretraining, multimodal data, alignment, applications, platform governance, compliance, and hands-on projects; Alt text: full fourteen-part lifecycle map showing the knowledge structure spanning general principles, pretraining, multimodal, alignment, applications, platform, compliance, and hands-on projects</x:v>
+        <x:v>Figure 1-2: Full Fourteen-Part Lifecycle Map. Source: original illustration. The figure uses infrastructure as its foundation, threading through pretraining, multimodal data, alignment, applications, platform governance, compliance, and hands-on projects</x:v>
       </x:c>
       <x:c r="J4" s="4" t="str">
         <x:v>Figure 1-2: Full Fourteen-Part Lifecycle Map, showing the knowledge structure spanning general principles, pretraining, multimodal, alignment, applications, platform, compliance, and hands-on projects</x:v>
@@ -1169,7 +1171,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O4" s="4" t="str">
-        <x:v>full fourteen-part lifecycle map showing the knowledge structure spanning general principles, pretraining, multimodal, alignment, applications, platform, compliance, and hands-on projects.</x:v>
+        <x:v>Full Fourteen-Part Lifecycle Map. Source: original illustration. The figure uses infrastructure as its foundation, threading through pretraining, multimodal data, alignment, applications, platform governance, compliance, and hands-on projects.</x:v>
       </x:c>
       <x:c r="P4" s="4" t="str"/>
       <x:c r="Q4" s="4" t="str">
@@ -1181,7 +1183,7 @@
       <x:c r="S4" s="4" t="str"/>
       <x:c r="T4" s="4" t="str"/>
       <x:c r="U4" s="4" t="str">
-        <x:v>图1-2：全书十四篇制生命周期地图。来源：本书自绘。该图以基础设施为底座，串联预训练、多模态、对齐、应用、平台治理、合规与项目实战；Alt text：全书十四篇制生命周期地图，展示从总论、预训练、多模态、对齐、应用、平台、合规到项目实战的知识结构</x:v>
+        <x:v>图1-2：全书十四篇制生命周期地图。来源：本书自绘。该图以基础设施为底座，串联预训练、多模态、对齐、应用、平台治理、合规与项目实战</x:v>
       </x:c>
       <x:c r="V4" s="4" t="str">
         <x:v>图1-2：全书十四篇制生命周期地图，展示从总论、预训练、多模态、对齐、应用、平台、合规到项目实战的知识结构</x:v>
@@ -1213,7 +1215,7 @@
         <x:v>2-1</x:v>
       </x:c>
       <x:c r="I5" s="4" t="str">
-        <x:v>Figure 2-1: Multi-dimensional quality layering architecture from a lifecycle perspective. Source: original illustration from this book. The upper half is a horizontal four-stage pipeline: pre-training (scale/diversity/low duplication), SFT (instruction coverage/format compliance/factual accuracy), RLHF/DPO preference alignment (contrastive signal/annotation consistency/value alignment), and RAG application (timeliness/retrieval accuracy/traceability); the lower half is a triangular mapping structure showing the bidirectional relationships among offline data quality, proxy model evaluation, and real online business metrics. Alt text: horizontal four-stage pipeline diagram from pre-training to RAG application showing key quality metrics at each stage; the triangle below shows the relationships among offline data quality, proxy model evaluation, and real business metrics</x:v>
+        <x:v>Figure 2-1: Multi-dimensional quality layering architecture from a lifecycle perspective. Source: original illustration from this book. The upper half is a horizontal four-stage pipeline: pre-training (scale/diversity/low duplication), SFT (instruction coverage/format compliance/factual accuracy), RLHF/DPO preference alignment (contrastive signal/annotation consistency/value alignment), and RAG application (timeliness/retrieval accuracy/traceability); the lower half is a triangular mapping structure showing the bidirectional relationships among offline data quality, proxy model evaluation, and real online business metrics</x:v>
       </x:c>
       <x:c r="J5" s="4" t="str">
         <x:v>Figure 2-1: Multi-dimensional quality layering architecture from a lifecycle perspective, showing how metric weights shift across stages from scale and diversity toward truthfulness and helpfulness</x:v>
@@ -1231,7 +1233,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O5" s="4" t="str">
-        <x:v>horizontal four-stage pipeline diagram from pre-training to RAG application showing key quality metrics at each stage; the triangle below shows the relationships among offline data quality, proxy model evaluation, and real business metrics.</x:v>
+        <x:v>Multi-dimensional quality layering architecture from a lifecycle perspective. Source: original illustration from this book. The upper half is a horizontal four-stage pipeline: pre-training (scale/diversity/low duplication), SFT (instruction coverage/format compliance/factual accuracy), RLHF/DPO preference alignment (contrastive signal/annotation consistency/value alignment), and RAG application (timeliness/retrieval accuracy/traceability); the lower half is a triangular ma...</x:v>
       </x:c>
       <x:c r="P5" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Chapter 2: LLM Data Lifecycle and Quality Evaluation Framework; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -1245,7 +1247,7 @@
       <x:c r="S5" s="4" t="str"/>
       <x:c r="T5" s="4" t="str"/>
       <x:c r="U5" s="4" t="str">
-        <x:v>图2-1：生命周期视角下的多维度质量分层架构。来源：本书自绘。上半部分为水平四阶段流水线：预训练（规模/多样性/低重复率）→ 指令微调SFT（指令覆盖/格式合规/事实准确）→ 偏好对齐RLHF/DPO（对比信号/标注一致性/价值观贴合）→ RAG应用（时效性/检索精度/可追溯性）；下半部分为三角映射结构，展示离线数据质量、代理模型评测和真实业务在线三者的双向关联。Alt text：水平四阶段流水线图，从预训练到RAG应用展示各阶段关键质量指标；下方三角形展示离线数据质量、代理模型评测与真实业务指标的相互关系</x:v>
+        <x:v>图2-1：生命周期视角下的多维度质量分层架构。来源：本书自绘。上半部分为水平四阶段流水线：预训练（规模/多样性/低重复率）→ 指令微调SFT（指令覆盖/格式合规/事实准确）→ 偏好对齐RLHF/DPO（对比信号/标注一致性/价值观贴合）→ RAG应用（时效性/检索精度/可追溯性）；下半部分为三角映射结构，展示离线数据质量、代理模型评测和真实业务在线三者的双向关联</x:v>
       </x:c>
       <x:c r="V5" s="4" t="str">
         <x:v>图2-1：生命周期视角下的多维度质量分层架构，展示不同阶段质量指标权重从规模、多样性转向真实性、帮助性</x:v>
@@ -1277,7 +1279,7 @@
         <x:v>2-2</x:v>
       </x:c>
       <x:c r="I6" s="4" t="str">
-        <x:v>Figure 2-2: Cross-mapping matrix of large language model data defects and quality metrics. Source: original illustration from this book. The matrix rows are six defect classes: noise, repetition, benchmark contamination, systematic bias, structural incompleteness, and staleness; the columns are five quality metrics: accuracy, consistency, diversity, coverage, and traceability. Each cell uses a filled circle (strong impact), half circle (medium impact), or empty circle (weak impact) to mark impact strength. Alt text: 6-by-5 cross-mapping matrix with six data defect classes as rows and five quality metrics as columns; each cell uses a filled circle, half circle, or empty circle to indicate impact strength, with a legend for the three symbols at the bottom</x:v>
+        <x:v>Figure 2-2: Cross-mapping matrix of large language model data defects and quality metrics. Source: original illustration from this book. The matrix rows are six defect classes: noise, repetition, benchmark contamination, systematic bias, structural incompleteness, and staleness; the columns are five quality metrics: accuracy, consistency, diversity, coverage, and traceability. Each cell uses a filled circle (strong impact), half circle (medium impact), or empty circle (weak impact) to mark impact strength</x:v>
       </x:c>
       <x:c r="J6" s="4" t="str">
         <x:v>Figure 2-2: Cross-mapping diagram of large language model data defects and quality metrics, showing the relationships between six defect classes and accuracy, consistency, diversity, coverage, and traceability</x:v>
@@ -1295,7 +1297,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O6" s="4" t="str">
-        <x:v>6-by-5 cross-mapping matrix with six data defect classes as rows and five quality metrics as columns; each cell uses a filled circle, half circle, or empty circle to indicate impact strength, with a legend for the three symbols at the bottom.</x:v>
+        <x:v>Cross-mapping matrix of large language model data defects and quality metrics. Source: original illustration from this book. The matrix rows are six defect classes: noise, repetition, benchmark contamination, systematic bias, structural incompleteness, and staleness; the columns are five quality metrics: accuracy, consistency, diversity, coverage, and traceability. Each cell uses a filled circle (strong impact), half circle (medium impact), or empty circle (weak impact) to...</x:v>
       </x:c>
       <x:c r="P6" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Chapter 2: LLM Data Lifecycle and Quality Evaluation Framework; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -1309,7 +1311,7 @@
       <x:c r="S6" s="4" t="str"/>
       <x:c r="T6" s="4" t="str"/>
       <x:c r="U6" s="4" t="str">
-        <x:v>图2-2：大模型数据缺陷与质量指标交叉映射矩阵。来源：本书自绘。矩阵行为六类缺陷：噪声、重复、基准污染、系统偏差、结构缺失、时效衰败；矩阵列为五项质量指标：准确度、一致性、多样性、覆盖度、可追溯性。各单元格以实心圆（强影响）、半圆（中等影响）、空圆（弱影响）标注影响程度。Alt text：6行×5列交叉映射矩阵，行为六类数据缺陷，列为五项质量指标，每个单元格用实心圆、半圆或空圆表示影响强弱；底部附图例说明三种符号含义</x:v>
+        <x:v>图2-2：大模型数据缺陷与质量指标交叉映射矩阵。来源：本书自绘。矩阵行为六类缺陷：噪声、重复、基准污染、系统偏差、结构缺失、时效衰败；矩阵列为五项质量指标：准确度、一致性、多样性、覆盖度、可追溯性。各单元格以实心圆（强影响）、半圆（中等影响）、空圆（弱影响）标注影响程度</x:v>
       </x:c>
       <x:c r="V6" s="4" t="str">
         <x:v>图2-2：大模型数据缺陷与质量指标交叉映射图，展示六类缺陷与准确度、一致性、多样性、覆盖度和可追溯性之间的关系</x:v>
@@ -1341,7 +1343,7 @@
         <x:v>2-3</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
-        <x:v>Figure 2-3: Automated blocking and governance flow driven by the data scorecard. Source: original illustration from this book. The figure shows how hard gates, soft gates, manual review, and rollback actions collectively block contaminated or degraded data samples; Alt text: automated blocking and governance flow driven by the data scorecard, showing hard gates, soft gates, manual review, and rollback actions</x:v>
+        <x:v>Figure 2-3: Automated blocking and governance flow driven by the data scorecard. Source: original illustration from this book. The figure shows how hard gates, soft gates, manual review, and rollback actions collectively block contaminated or degraded data samples</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
         <x:v>Figure 2-3: Automated blocking and governance flow driven by the data scorecard, showing hard gates, soft gates, manual review, and rollback actions</x:v>
@@ -1359,7 +1361,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O7" s="4" t="str">
-        <x:v>automated blocking and governance flow driven by the data scorecard, showing hard gates, soft gates, manual review, and rollback actions.</x:v>
+        <x:v>Automated blocking and governance flow driven by the data scorecard. Source: original illustration from this book. The figure shows how hard gates, soft gates, manual review, and rollback actions collectively block contaminated or degraded data samples.</x:v>
       </x:c>
       <x:c r="P7" s="4" t="str"/>
       <x:c r="Q7" s="4" t="str">
@@ -1371,7 +1373,7 @@
       <x:c r="S7" s="4" t="str"/>
       <x:c r="T7" s="4" t="str"/>
       <x:c r="U7" s="4" t="str">
-        <x:v>图2-3：数据评分卡驱动的自动截断与治理流。来源：本书自绘。该图展示硬闸门、软闸门、人工复核和回滚动作如何共同阻隔被污染或劣化的数据样本；Alt text：数据评分卡驱动的自动截断与治理流，展示硬闸门、软闸门、人工复核和回滚动作</x:v>
+        <x:v>图2-3：数据评分卡驱动的自动截断与治理流。来源：本书自绘。该图展示硬闸门、软闸门、人工复核和回滚动作如何共同阻隔被污染或劣化的数据样本</x:v>
       </x:c>
       <x:c r="V7" s="4" t="str">
         <x:v>图2-3：数据评分卡驱动的自动截断与治理流，展示硬闸门、软闸门、人工复核和回滚动作</x:v>
@@ -1403,7 +1405,7 @@
         <x:v>3-1</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>Figure 3-1: Five-layer architecture of an AI-native data stack. Source: original illustration from this book. The figure shows how ingestion and access, processing orchestration, storage and indexing, evaluation operations, and governance and security layers jointly move data from raw corpus to trainable datasets; Alt text: five-layer architecture of an AI-native data stack showing the data flow among ingestion and access, processing orchestration, storage and indexing, evaluation operations, and governance and security layers</x:v>
+        <x:v>Figure 3-1: Five-layer architecture of an AI-native data stack. Source: original illustration from this book. The figure shows how ingestion and access, processing orchestration, storage and indexing, evaluation operations, and governance and security layers jointly move data from raw corpus to trainable datasets</x:v>
       </x:c>
       <x:c r="J8" s="4" t="str">
         <x:v>Figure 3-1: Five-layer architecture of an AI-native data stack</x:v>
@@ -1421,7 +1423,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O8" s="4" t="str">
-        <x:v>five-layer architecture of an AI-native data stack showing the data flow among ingestion and access, processing orchestration, storage and indexing, evaluation operations, and governance and security layers.</x:v>
+        <x:v>Five-layer architecture of an AI-native data stack. Source: original illustration from this book. The figure shows how ingestion and access, processing orchestration, storage and indexing, evaluation operations, and governance and security layers jointly move data from raw corpus to trainable datasets.</x:v>
       </x:c>
       <x:c r="P8" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Chapter 3: AI-Native Data Stack and Cost Governance; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -1435,7 +1437,7 @@
       <x:c r="S8" s="4" t="str"/>
       <x:c r="T8" s="4" t="str"/>
       <x:c r="U8" s="4" t="str">
-        <x:v>图3-1：AI 原生数据栈五层架构。来源：本书自绘。该图展示采集接入、处理编排、存储索引、评测运营和治理安全层如何协同驱动数据从原始语料流向可训练数据集；Alt text：AI 原生数据栈五层架构，展示采集接入、处理编排、存储索引、评测运营和治理安全层之间的数据流</x:v>
+        <x:v>图3-1：AI 原生数据栈五层架构。来源：本书自绘。该图展示采集接入、处理编排、存储索引、评测运营和治理安全层如何协同驱动数据从原始语料流向可训练数据集</x:v>
       </x:c>
       <x:c r="V8" s="4" t="str">
         <x:v>图3-1：AI原生数据栈五层架构，展示采集接入、处理编排、存储索引、评测运营和治理安全层之间的数据流</x:v>
@@ -1467,7 +1469,7 @@
         <x:v>3-2</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>Figure 3-2: Training-data cost-governance loop. Source: original illustration from this book. The figure shows a cross-version iteration cycle that starts from budget planning, passes through cost monitoring, ROI evaluation, and optimization decisions, and returns to budget review; Alt text: training-data cost-governance loop showing the cycle of budget planning, cost monitoring, ROI evaluation, optimization decisions, and budget review</x:v>
+        <x:v>Figure 3-2: Training-data cost-governance loop. Source: original illustration from this book. The figure shows a cross-version iteration cycle that starts from budget planning, passes through cost monitoring, ROI evaluation, and optimization decisions, and returns to budget review</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
         <x:v>Figure 3-2: Training-data cost-governance loop</x:v>
@@ -1485,7 +1487,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O9" s="4" t="str">
-        <x:v>training-data cost-governance loop showing the cycle of budget planning, cost monitoring, ROI evaluation, optimization decisions, and budget review.</x:v>
+        <x:v>Training-data cost-governance loop. Source: original illustration from this book. The figure shows a cross-version iteration cycle that starts from budget planning, passes through cost monitoring, ROI evaluation, and optimization decisions, and returns to budget review.</x:v>
       </x:c>
       <x:c r="P9" s="4" t="str"/>
       <x:c r="Q9" s="4" t="str">
@@ -1497,7 +1499,7 @@
       <x:c r="S9" s="4" t="str"/>
       <x:c r="T9" s="4" t="str"/>
       <x:c r="U9" s="4" t="str">
-        <x:v>图3-2：训练数据成本治理闭环。来源：本书自绘。该图展示从预算规划出发，经过成本监控、ROI 评估和优化决策，最终回归预算复盘的跨版本迭代过程；Alt text：训练数据成本治理闭环图，展示预算规划、成本监控、ROI 评估、优化决策和预算复盘的循环</x:v>
+        <x:v>图3-2：训练数据成本治理闭环。来源：本书自绘。该图展示从预算规划出发，经过成本监控、ROI 评估和优化决策，最终回归预算复盘的跨版本迭代过程</x:v>
       </x:c>
       <x:c r="V9" s="4" t="str">
         <x:v>图3-2：训练数据成本治理闭环图，展示预算规划、成本监控、ROI评估、优化决策和预算复盘的循环</x:v>
@@ -1529,7 +1531,7 @@
         <x:v>4-1</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>Figure 4-1: Layered map of pre-training data sources. The three-layer taxonomy positions mainstream sources by processing complexity, knowledge density, and license risk, with typical reference ranges for mixing. Source: original illustration from this book; Alt text: layered map of pretraining data sources showing the quality and compliance positions of open web, forums and Q&amp;A, encyclopedias, code, academic papers, books, enterprise internal data, and user feedback data</x:v>
+        <x:v>Figure 4-1: Layered map of pre-training data sources. The three-layer taxonomy positions mainstream sources by processing complexity, knowledge density, and license risk, with typical reference ranges for mixing. Source: original illustration from this book</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
         <x:v>Figure 4-1: Layered map of pre-training data sources</x:v>
@@ -1547,7 +1549,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O10" s="4" t="str">
-        <x:v>layered map of pretraining data sources showing the quality and compliance positions of open web, forums and Q&amp;A, encyclopedias, code, academic papers, books, enterprise internal data, and user feedback data.</x:v>
+        <x:v>Layered map of pre-training data sources. The three-layer taxonomy positions mainstream sources by processing complexity, knowledge density, and license risk, with typical reference ranges for mixing. Source: original illustration from this book.</x:v>
       </x:c>
       <x:c r="P10" s="4" t="str"/>
       <x:c r="Q10" s="4" t="str">
@@ -1559,7 +1561,7 @@
       <x:c r="S10" s="4" t="str"/>
       <x:c r="T10" s="4" t="str"/>
       <x:c r="U10" s="4" t="str">
-        <x:v>图4-1：预训练数据源分层地图 —— 三层分类体系按照处理复杂度、知识密度和许可风险对主流数据来源进行定位，并给出典型的配比参考区间。来源：本书自绘；Alt text：预训练数据源分层地图，展示开放网页、论坛问答、百科、代码、学术论文、书籍、企业内部数据和用户反馈数据的质量与合规位置</x:v>
+        <x:v>图4-1：预训练数据源分层地图 —— 三层分类体系按照处理复杂度、知识密度和许可风险对主流数据来源进行定位，并给出典型的配比参考区间。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V10" s="4" t="str">
         <x:v>图4-1：预训练数据源分层地图</x:v>
@@ -1591,7 +1593,7 @@
         <x:v>4-2</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>Figure 4-2: Data ingestion and provenance chain. From source contact to final archive, each processing stage appends metadata records to the "Provenance Ledger," forming a complete auditable data-lineage chain. Source: original illustration from this book; Alt text: data ingestion and provenance chain diagram showing the links among source contact, acquisition, parsing, cleaning, storage, and audit records</x:v>
+        <x:v>Figure 4-2: Data ingestion and provenance chain. From source contact to final archive, each processing stage appends metadata records to the "Provenance Ledger," forming a complete auditable data-lineage chain. Source: original illustration from this book</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
         <x:v>Figure 4-2: Data ingestion and provenance chain</x:v>
@@ -1609,7 +1611,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O11" s="4" t="str">
-        <x:v>data ingestion and provenance chain diagram showing the links among source contact, acquisition, parsing, cleaning, storage, and audit records.</x:v>
+        <x:v>Data ingestion and provenance chain. From source contact to final archive, each processing stage appends metadata records to the "Provenance Ledger," forming a complete auditable data-lineage chain. Source: original illustration from this book.</x:v>
       </x:c>
       <x:c r="P11" s="4" t="str"/>
       <x:c r="Q11" s="4" t="str">
@@ -1621,7 +1623,7 @@
       <x:c r="S11" s="4" t="str"/>
       <x:c r="T11" s="4" t="str"/>
       <x:c r="U11" s="4" t="str">
-        <x:v>图4-2：数据采集与权属存证流程——从数据源触达到最终归档，每个处理阶段均向"Provenance Ledger（权属账本）"追加元数据记录，形成完整的可审计数据血缘链路。来源：本书自绘；Alt text：数据采集与权属存证流程图，展示来源触达、采集、解析、清洗、入库和审计记录之间的链路</x:v>
+        <x:v>图4-2：数据采集与权属存证流程——从数据源触达到最终归档，每个处理阶段均向"Provenance Ledger（权属账本）"追加元数据记录，形成完整的可审计数据血缘链路。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V11" s="4" t="str">
         <x:v>图4-2：数据采集与权属存证流程图</x:v>
@@ -1653,7 +1655,7 @@
         <x:v>5-1</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>Figure 5-1: Overview Flowchart of the Cleaning and Decontamination Pipeline — A multi-stage quality gate gradually refines raw corpus into candidate training corpus. The proportions in the figure are illustrative only; real retention rates depend on source quality, filtering thresholds, and compliance requirements. Source: original illustration from this book; Alt text: overview flowchart of the cleaning and decontamination pipeline, showing the sequential relationship among rule-based filtering, model scoring, deduplication, PII redaction, decontamination, and manual spot-checks</x:v>
+        <x:v>Figure 5-1: Overview Flowchart of the Cleaning and Decontamination Pipeline — A multi-stage quality gate gradually refines raw corpus into candidate training corpus. The proportions in the figure are illustrative only; real retention rates depend on source quality, filtering thresholds, and compliance requirements. Source: original illustration from this book</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
         <x:v>Figure 5-1: Overview Flowchart of the Cleaning and Decontamination Pipeline</x:v>
@@ -1671,7 +1673,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O12" s="4" t="str">
-        <x:v>overview flowchart of the cleaning and decontamination pipeline, showing the sequential relationship among rule-based filtering, model scoring, deduplication, PII redaction, decontamination, and manual spot-checks.</x:v>
+        <x:v>Overview Flowchart of the Cleaning and Decontamination Pipeline — A multi-stage quality gate gradually refines raw corpus into candidate training corpus. The proportions in the figure are illustrative only; real retention rates depend on source quality, filtering thresholds, and compliance requirements. Source: original illustration from this book.</x:v>
       </x:c>
       <x:c r="P12" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Chapter 5: Cleaning, Deduplication, and Decontamination; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -1685,7 +1687,7 @@
       <x:c r="S12" s="4" t="str"/>
       <x:c r="T12" s="4" t="str"/>
       <x:c r="U12" s="4" t="str">
-        <x:v>图5-1：清洗与去污染全景流程图 —— 多阶段质量闸门从原始语料逐步精炼为候选训练语料，图中比例仅为示意，真实留存率取决于来源质量、过滤阈值和合规要求。来源：本书自绘；Alt text：清洗与去污染全景流程图，展示规则过滤、模型评分、去重、PII 脱敏、去污染和人工抽检的顺序关系</x:v>
+        <x:v>图5-1：清洗与去污染全景流程图 —— 多阶段质量闸门从原始语料逐步精炼为候选训练语料，图中比例仅为示意，真实留存率取决于来源质量、过滤阈值和合规要求。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V12" s="4" t="str">
         <x:v>图5-1：清洗与去污染全景流程图</x:v>
@@ -1717,7 +1719,7 @@
         <x:v>5-2</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>Figure 5-2: Quality Filtering Funnel and Spot-Check Feedback Loop — The funnel on the left shows the data retention rate at each stage; the feedback loop on the right shows how manual spot-checks drive continuous iterative optimization of filtering rules. Source: original illustration; Alt text: Quality filtering funnel and spot-check feedback loop diagram, showing the cyclic relationship among rule-based filtering, model scoring, deduplication, manual spot-checks, and rule write-back</x:v>
+        <x:v>Figure 5-2: Quality Filtering Funnel and Spot-Check Feedback Loop — The funnel on the left shows the data retention rate at each stage; the feedback loop on the right shows how manual spot-checks drive continuous iterative optimization of filtering rules. Source: original illustration</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
         <x:v>Figure 5-2: Quality Filtering Funnel and Spot-Check Feedback Loop</x:v>
@@ -1735,7 +1737,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O13" s="4" t="str">
-        <x:v>Quality filtering funnel and spot-check feedback loop diagram, showing the cyclic relationship among rule-based filtering, model scoring, deduplication, manual spot-checks, and rule write-back.</x:v>
+        <x:v>Quality Filtering Funnel and Spot-Check Feedback Loop — The funnel on the left shows the data retention rate at each stage; the feedback loop on the right shows how manual spot-checks drive continuous iterative optimization of filtering rules. Source: original illustration.</x:v>
       </x:c>
       <x:c r="P13" s="4" t="str"/>
       <x:c r="Q13" s="4" t="str">
@@ -1747,7 +1749,7 @@
       <x:c r="S13" s="4" t="str"/>
       <x:c r="T13" s="4" t="str"/>
       <x:c r="U13" s="4" t="str">
-        <x:v>图5-2：质量过滤漏斗与抽检闭环 —— 左侧漏斗展示每阶段的数据留存率，右侧闭环展示人工抽检如何驱动过滤规则的持续迭代优化。来源：本书自绘；Alt text：质量过滤漏斗与抽检闭环图，展示规则过滤、模型评分、去重、人工抽检和规则回写之间的循环关系</x:v>
+        <x:v>图5-2：质量过滤漏斗与抽检闭环 —— 左侧漏斗展示每阶段的数据留存率，右侧闭环展示人工抽检如何驱动过滤规则的持续迭代优化。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V13" s="4" t="str">
         <x:v>图5-2：质量过滤漏斗与抽检闭环图</x:v>
@@ -1779,7 +1781,7 @@
         <x:v>6-1</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>Figure 6-1: Throughput bottleneck diagnosis flowchart — starting from abnormal GPU utilization, a three-level decision tree is used to locate disk I/O bottlenecks, CPU preprocessing bottlenecks, and PCIe transfer bottlenecks, with corresponding remediation steps. Source: original illustration from this book; Alt text: throughput bottleneck diagnosis flowchart showing the decision paths from abnormal GPU utilization to disk I/O, CPU preprocessing, and PCIe transfer investigation</x:v>
+        <x:v>Figure 6-1: Throughput bottleneck diagnosis flowchart — starting from abnormal GPU utilization, a three-level decision tree is used to locate disk I/O bottlenecks, CPU preprocessing bottlenecks, and PCIe transfer bottlenecks, with corresponding remediation steps. Source: original illustration from this book</x:v>
       </x:c>
       <x:c r="J14" s="4" t="str">
         <x:v>Figure 6-1: Throughput Bottleneck Diagnosis Flowchart</x:v>
@@ -1797,7 +1799,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O14" s="4" t="str">
-        <x:v>throughput bottleneck diagnosis flowchart showing the decision paths from abnormal GPU utilization to disk I/O, CPU preprocessing, and PCIe transfer investigation.</x:v>
+        <x:v>Throughput bottleneck diagnosis flowchart — starting from abnormal GPU utilization, a three-level decision tree is used to locate disk I/O bottlenecks, CPU preprocessing bottlenecks, and PCIe transfer bottlenecks, with corresponding remediation steps. Source: original illustration from this book.</x:v>
       </x:c>
       <x:c r="P14" s="4" t="str"/>
       <x:c r="Q14" s="4" t="str">
@@ -1809,7 +1811,7 @@
       <x:c r="S14" s="4" t="str"/>
       <x:c r="T14" s="4" t="str"/>
       <x:c r="U14" s="4" t="str">
-        <x:v>图6-1：吞吐瓶颈诊断流程图 —— 从 GPU 利用率异常出发，通过三级决策树定位磁盘 I/O 瓶颈、CPU 预处理瓶颈和 PCIe 传输瓶颈，并给出对应的修复方案。来源：本书自绘；Alt text：吞吐瓶颈诊断流程图，展示从 GPU 利用率异常到磁盘 I/O、CPU 预处理和 PCIe 传输排查的决策路径</x:v>
+        <x:v>图6-1：吞吐瓶颈诊断流程图 —— 从 GPU 利用率异常出发，通过三级决策树定位磁盘 I/O 瓶颈、CPU 预处理瓶颈和 PCIe 传输瓶颈，并给出对应的修复方案。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V14" s="4" t="str">
         <x:v>图6-1：吞吐瓶颈诊断流程图</x:v>
@@ -1841,7 +1843,7 @@
         <x:v>6-2</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>Figure 6-2: LLM training input pipeline layered architecture — the complete five-stage path from tokenization, serialization, data mixing, and packing to DataLoader GPU feeding, with the two highest-frequency bottleneck risk points (disk I/O and CPU-GPU transfer) annotated at the bottom. Source: original illustration from this book; Alt text: training input pipeline layer diagram showing the sequential relationship between tokenization, serialization, mixing, packing, DataLoader, and GPU feeding</x:v>
+        <x:v>Figure 6-2: LLM training input pipeline layered architecture — the complete five-stage path from tokenization, serialization, data mixing, and packing to DataLoader GPU feeding, with the two highest-frequency bottleneck risk points (disk I/O and CPU-GPU transfer) annotated at the bottom. Source: original illustration from this book</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
         <x:v>Figure 6-2: Training Input Pipeline Layer Diagram</x:v>
@@ -1859,7 +1861,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O15" s="4" t="str">
-        <x:v>training input pipeline layer diagram showing the sequential relationship between tokenization, serialization, mixing, packing, DataLoader, and GPU feeding.</x:v>
+        <x:v>LLM training input pipeline layered architecture — the complete five-stage path from tokenization, serialization, data mixing, and packing to DataLoader GPU feeding, with the two highest-frequency bottleneck risk points (disk I/O and CPU-GPU transfer) annotated at the bottom. Source: original illustration from this book.</x:v>
       </x:c>
       <x:c r="P15" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Chapter 6: Tokenization, Serialization, and Efficient Loading; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -1873,7 +1875,7 @@
       <x:c r="S15" s="4" t="str"/>
       <x:c r="T15" s="4" t="str"/>
       <x:c r="U15" s="4" t="str">
-        <x:v>图6-2：LLM 训练输入管道分层架构 —— 从分词、序列化、数据混采、Packing 到 DataLoader GPU 馈送的五阶段完整路径，底部标注了两个最高频的瓶颈风险点（磁盘 I/O 和 CPU↔GPU 传输）。来源：本书自绘；Alt text：训练输入管道分层图，展示分词、序列化、混采、Packing、DataLoader 和 GPU 馈送之间的顺序关系</x:v>
+        <x:v>图6-2：LLM 训练输入管道分层架构 —— 从分词、序列化、数据混采、Packing 到 DataLoader GPU 馈送的五阶段完整路径，底部标注了两个最高频的瓶颈风险点（磁盘 I/O 和 CPU↔GPU 传输）。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V15" s="4" t="str">
         <x:v>图6-2：训练输入管道分层图</x:v>
@@ -1905,7 +1907,7 @@
         <x:v>7-1</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>Figure 7-1: Data Operations Flywheel — The left side shows the high-cost startup zone; the right side shows the gradually accumulated cycle of automated, high-quality data assets formed after long-term model evaluation and root-cause analysis feedback. Source: Original illustration by the authors. Alt text: Data operations flywheel diagram showing the cyclical relationship among data production, model evaluation, root-cause analysis, rule write-back, and asset reuse</x:v>
+        <x:v>Figure 7-1: Data Operations Flywheel — The left side shows the high-cost startup zone; the right side shows the gradually accumulated cycle of automated, high-quality data assets formed after long-term model evaluation and root-cause analysis feedback. Source: Original illustration by the authors</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
         <x:v>Figure 7-1: Data Operations Flywheel</x:v>
@@ -1923,7 +1925,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O16" s="4" t="str">
-        <x:v>Data operations flywheel diagram showing the cyclical relationship among data production, model evaluation, root-cause analysis, rule write-back, and asset reuse.</x:v>
+        <x:v>Data Operations Flywheel — The left side shows the high-cost startup zone; the right side shows the gradually accumulated cycle of automated, high-quality data assets formed after long-term model evaluation and root-cause analysis feedback. Source: Original illustration by the authors.</x:v>
       </x:c>
       <x:c r="P16" s="4" t="str"/>
       <x:c r="Q16" s="4" t="str">
@@ -1935,7 +1937,7 @@
       <x:c r="S16" s="4" t="str"/>
       <x:c r="T16" s="4" t="str"/>
       <x:c r="U16" s="4" t="str">
-        <x:v>图7-1：数据运营飞轮图 —— 左侧展示高成本的起步区，右侧展示经过长期模型评估与根因分析反哺后，逐渐形成的自动化、高质量数据资产积累循环。来源：本书自绘；Alt text：数据运营飞轮图，展示数据生产、模型评估、根因分析、规则回写和资产复用之间的循环关系</x:v>
+        <x:v>图7-1：数据运营飞轮图 —— 左侧展示高成本的起步区，右侧展示经过长期模型评估与根因分析反哺后，逐渐形成的自动化、高质量数据资产积累循环。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V16" s="4" t="str">
         <x:v>图7-1：数据运营飞轮图</x:v>
@@ -1967,7 +1969,7 @@
         <x:v>7-2</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>Figure 7-2: Data Evaluation Feedback Loop — A circular architecture proceeding from sampling-based blind review to root-cause investigation triggered by metric anomalies, followed by targeted system governance actions. Source: Original illustration by the authors. Alt text: Data evaluation feedback loop diagram showing the closed-loop relationship among sampling evaluation, metric anomalies, root-cause investigation, governance actions, and rule updates</x:v>
+        <x:v>Figure 7-2: Data Evaluation Feedback Loop — A circular architecture proceeding from sampling-based blind review to root-cause investigation triggered by metric anomalies, followed by targeted system governance actions. Source: Original illustration by the authors</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
         <x:v>Figure 7-2: Data Evaluation Feedback Loop</x:v>
@@ -1985,9 +1987,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O17" s="4" t="str">
-        <x:v>Data evaluation feedback loop diagram showing the closed-loop relationship among sampling evaluation, metric anomalies, root-cause investigation, governance actions, and rule updates.</x:v>
-      </x:c>
-      <x:c r="P17" s="4" t="str"/>
+        <x:v>Data Evaluation Feedback Loop — A circular architecture proceeding from sampling-based blind review to root-cause investigation triggered by metric anomalies, followed by targeted system governance actions. Source: Original illustration by the authors.</x:v>
+      </x:c>
+      <x:c r="P17" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 7: Data Evaluation, Quality Closed Loop, and Operational Iteration; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q17" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -1997,7 +2001,7 @@
       <x:c r="S17" s="4" t="str"/>
       <x:c r="T17" s="4" t="str"/>
       <x:c r="U17" s="4" t="str">
-        <x:v>图7-2：数据评估闭环图 —— 从抽取式盲审到针对评估指标启动根因排查，再针对具体现象采取系统治理动作的环形架构。来源：本书自绘；Alt text：数据评估闭环图，展示抽样评估、指标异常、根因排查、治理动作和规则更新之间的闭环</x:v>
+        <x:v>图7-2：数据评估闭环图 —— 从抽取式盲审到针对评估指标启动根因排查，再针对具体现象采取系统治理动作的环形架构。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V17" s="4" t="str">
         <x:v>图7-2：数据评估闭环图</x:v>
@@ -2029,7 +2033,7 @@
         <x:v>8-1</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>Figure 8-1: Overview of multimodal image-text data engineering. The pipeline starts from DOM-tree crawling and PDF parsing, then moves through format parsing, watermark filtering, CLIP semantic alignment, interleaved-sequence assembly, and tokenized representation. Distributed computing and metadata form the foundation across the pipeline. Source: drawn for this book. Alt text: an overview of image-text data engineering showing DOM extraction, image download, format parsing, filtering, semantic alignment, recaptioning, and sequence assembly</x:v>
+        <x:v>Figure 8-1: Overview of multimodal image-text data engineering. The pipeline starts from DOM-tree crawling and PDF parsing, then moves through format parsing, watermark filtering, CLIP semantic alignment, interleaved-sequence assembly, and tokenized representation. Distributed computing and metadata form the foundation across the pipeline. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
         <x:v>Figure 8-1: Overview of image-text data engineering</x:v>
@@ -2047,9 +2051,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O18" s="4" t="str">
-        <x:v>an overview of image-text data engineering showing DOM extraction, image download, format parsing, filtering, semantic alignment, recaptioning, and sequence assembly.</x:v>
-      </x:c>
-      <x:c r="P18" s="4" t="str"/>
+        <x:v>Overview of multimodal image-text data engineering. The pipeline starts from DOM-tree crawling and PDF parsing, then moves through format parsing, watermark filtering, CLIP semantic alignment, interleaved-sequence assembly, and tokenized representation. Distributed computing and metadata form the foundation across the pipeline. Source: drawn for this book.</x:v>
+      </x:c>
+      <x:c r="P18" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 8: Image-Text Pair Data Engineering; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q18" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -2059,7 +2065,7 @@
       <x:c r="S18" s="4" t="str"/>
       <x:c r="T18" s="4" t="str"/>
       <x:c r="U18" s="4" t="str">
-        <x:v>图8-1：多模态图文数据工程全景图 —— 从最左侧的 DOM 树抓取与 PDF 解析起始，依次穿过格式解析、水印过滤、CLIP 语义对齐、直至最右侧的交错序列拼装与 Token 化表示。分布式计算与 Metadata 是横跨底层的核心支撑。来源：本书自绘；Alt text：图文数据工程全景图，展示 DOM 抽取、图片下载、格式解析、过滤、语义对齐、重标注和序列拼装之间的流程</x:v>
+        <x:v>图8-1：多模态图文数据工程全景图 —— 从最左侧的 DOM 树抓取与 PDF 解析起始，依次穿过格式解析、水印过滤、CLIP 语义对齐、直至最右侧的交错序列拼装与 Token 化表示。分布式计算与 Metadata 是横跨底层的核心支撑。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V18" s="4" t="str">
         <x:v>图8-1：图文数据工程全景图</x:v>
@@ -2091,7 +2097,7 @@
         <x:v>8-2</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>Figure 8-2: Image semantic alignment and filtering flow. A CLIP- and heuristic-rule-based quantitative decision tree filters out low-match samples, sends medium-match but high-value images to the recaptioning pipeline, and finally stores zero-padded or dynamically sliced images in the training pool. Source: drawn for this book. Alt text: an image semantic alignment and filtering flow showing quality filtering, CLIP scoring, recaptioning, dynamic slicing, and training-pool ingestion</x:v>
+        <x:v>Figure 8-2: Image semantic alignment and filtering flow. A CLIP- and heuristic-rule-based quantitative decision tree filters out low-match samples, sends medium-match but high-value images to the recaptioning pipeline, and finally stores zero-padded or dynamically sliced images in the training pool. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
         <x:v>Figure 8-2: Image semantic alignment and filtering flow</x:v>
@@ -2109,9 +2115,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O19" s="4" t="str">
-        <x:v>an image semantic alignment and filtering flow showing quality filtering, CLIP scoring, recaptioning, dynamic slicing, and training-pool ingestion.</x:v>
-      </x:c>
-      <x:c r="P19" s="4" t="str"/>
+        <x:v>Image semantic alignment and filtering flow. A CLIP- and heuristic-rule-based quantitative decision tree filters out low-match samples, sends medium-match but high-value images to the recaptioning pipeline, and finally stores zero-padded or dynamically sliced images in the training pool. Source: drawn for this book.</x:v>
+      </x:c>
+      <x:c r="P19" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 8: Image-Text Pair Data Engineering; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q19" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -2121,7 +2129,7 @@
       <x:c r="S19" s="4" t="str"/>
       <x:c r="T19" s="4" t="str"/>
       <x:c r="U19" s="4" t="str">
-        <x:v>图8-2：图像语义对齐与过滤流程图 —— 展示基于 CLIP 与启发式规则的量化决策树，将低匹配样本筛出，将中等匹配但高价值图片送往 Re-captioning 流水线，最后将图片 Zero-pad 或动态切分后存入训练池。来源：本书自绘；Alt text：图像语义对齐与过滤流程图，展示质量过滤、CLIP 打分、重标注、动态切分和训练池入库之间的路径</x:v>
+        <x:v>图8-2：图像语义对齐与过滤流程图 —— 展示基于 CLIP 与启发式规则的量化决策树，将低匹配样本筛出，将中等匹配但高价值图片送往 Re-captioning 流水线，最后将图片 Zero-pad 或动态切分后存入训练池。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V19" s="4" t="str">
         <x:v>图8-2：图像语义对齐与过滤流程图</x:v>
@@ -2153,7 +2161,7 @@
         <x:v>8-3</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>Figure 8-3: AnyRes dynamic multi-resolution patching. The core idea is that the high-resolution panoramic input on the left is no longer forced into a square. Instead, it is divided by an adaptive grid into $1 \times 3$ native-resolution local patches and paired with a global thumbnail in the upper-right corner before entering the vision encoder, preserving both high-frequency local features and global semantics. Source: drawn for this book. Alt text: AnyRes dynamic multi-resolution patching showing a panorama divided into local patches and combined with a global thumbnail</x:v>
+        <x:v>Figure 8-3: AnyRes dynamic multi-resolution patching. The core idea is that the high-resolution panoramic input on the left is no longer forced into a square. Instead, it is divided by an adaptive grid into $1 \times 3$ native-resolution local patches and paired with a global thumbnail in the upper-right corner before entering the vision encoder, preserving both high-frequency local features and global semantics. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
         <x:v>Figure 8-3: AnyRes dynamic multi-resolution patching</x:v>
@@ -2171,7 +2179,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O20" s="4" t="str">
-        <x:v>AnyRes dynamic multi-resolution patching showing a panorama divided into local patches and combined with a global thumbnail.</x:v>
+        <x:v>AnyRes dynamic multi-resolution patching. The core idea is that the high-resolution panoramic input on the left is no longer forced into a square. Instead, it is divided by an adaptive grid into $1 \times 3$ native-resolution local patches and paired with a global thumbnail in the upper-right corner before entering the vision encoder, preserving both high-frequency local features and global semantics. Source: drawn for this book.</x:v>
       </x:c>
       <x:c r="P20" s="4" t="str"/>
       <x:c r="Q20" s="4" t="str">
@@ -2183,7 +2191,7 @@
       <x:c r="S20" s="4" t="str"/>
       <x:c r="T20" s="4" t="str"/>
       <x:c r="U20" s="4" t="str">
-        <x:v>图8-3：AnyRes 动态多分辨率切割算法原理图 —— 展示 AnyRes 的核心思想：左侧的超长全景图（High-Res Input）不再被强制压缩，而是被自适应网格（Adaptive Grid）划分为 $1 \times 3$ 个原生分辨率的局部图像块（Local Patches），同时结合右上方全局缩略图（Global Thumbnail）一同送入 Vision Encoder，以保留高频局部特征与宏观语义。来源：本书自绘；Alt text：AnyRes 动态多分辨率切割算法原理图，展示全景图被切成局部块并与全局缩略图共同输入视觉编码器</x:v>
+        <x:v>图8-3：AnyRes 动态多分辨率切割算法原理图 —— 展示 AnyRes 的核心思想：左侧的超长全景图（High-Res Input）不再被强制压缩，而是被自适应网格（Adaptive Grid）划分为 $1 \times 3$ 个原生分辨率的局部图像块（Local Patches），同时结合右上方全局缩略图（Global Thumbnail）一同送入 Vision Encoder，以保留高频局部特征与宏观语义。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V20" s="4" t="str">
         <x:v>图8-3：AnyRes 动态多分辨率切割算法原理图</x:v>
@@ -2215,7 +2223,7 @@
         <x:v>9-1</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>Figure 9-1: Recaptioning and OCR dual-track enhancement. The left side shows a semantic vision track for dense narrative descriptions; the right side shows a structural text track containing DOM layout segmentation and table matrices. The two streams are fused into a unified hybrid supervision template. Source: drawn for this book. Alt text: a recaptioning and OCR dual-track enhancement diagram showing visual recaptioning, OCR structure extraction, BBox injection, and hybrid supervision</x:v>
+        <x:v>Figure 9-1: Recaptioning and OCR dual-track enhancement. The left side shows a semantic vision track for dense narrative descriptions; the right side shows a structural text track containing DOM layout segmentation and table matrices. The two streams are fused into a unified hybrid supervision template. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
         <x:v>Figure 9-1: Recaptioning and OCR dual-track enhancement</x:v>
@@ -2233,7 +2241,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O21" s="4" t="str">
-        <x:v>a recaptioning and OCR dual-track enhancement diagram showing visual recaptioning, OCR structure extraction, BBox injection, and hybrid supervision.</x:v>
+        <x:v>Recaptioning and OCR dual-track enhancement. The left side shows a semantic vision track for dense narrative descriptions; the right side shows a structural text track containing DOM layout segmentation and table matrices. The two streams are fused into a unified hybrid supervision template. Source: drawn for this book.</x:v>
       </x:c>
       <x:c r="P21" s="4" t="str"/>
       <x:c r="Q21" s="4" t="str">
@@ -2245,7 +2253,7 @@
       <x:c r="S21" s="4" t="str"/>
       <x:c r="T21" s="4" t="str"/>
       <x:c r="U21" s="4" t="str">
-        <x:v>图9-1：重标注与 OCR 增强联合的双轨管道图（Dual-track Pipeline） —— 左侧展示语义密集叙述流（Semantic Vision Track），右侧展示包含 DOM 排版分割与表格矩阵的高密度结构流（Structural Text Track），最终融合为统一的混合监督模板格式。来源：本书自绘；Alt text：重标注与 OCR 双流线增强图，展示视觉重描述、OCR 结构提取、BBox 注入和混合监督格式之间的关系</x:v>
+        <x:v>图9-1：重标注与 OCR 增强联合的双轨管道图（Dual-track Pipeline） —— 左侧展示语义密集叙述流（Semantic Vision Track），右侧展示包含 DOM 排版分割与表格矩阵的高密度结构流（Structural Text Track），最终融合为统一的混合监督模板格式。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V21" s="4" t="str">
         <x:v>图9-1：重标注与 OCR 双流线增强图</x:v>
@@ -2277,7 +2285,7 @@
         <x:v>9-2</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>Figure 9-2: Document structure layout-to-token mapping. The left side shows a fragment of a two-column academic report. The system first uses bounding-box arrays to locate titles, body text, charts, and formula regions. The right side shows how outputs from specialized models such as Nougat and PaddleOCR are post-processed into hierarchical Markdown text and rich text streams with discrete coordinates [xy]. Source: drawn for this book. Alt text: document layout-to-token mapping showing a page converted by layout detection, OCR, formula parsing, and coordinate labeling into hierarchical text</x:v>
+        <x:v>Figure 9-2: Document structure layout-to-token mapping. The left side shows a fragment of a two-column academic report. The system first uses bounding-box arrays to locate titles, body text, charts, and formula regions. The right side shows how outputs from specialized models such as Nougat and PaddleOCR are post-processed into hierarchical Markdown text and rich text streams with discrete coordinates [xy]. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J22" s="4" t="str">
         <x:v>Figure 9-2: Document structure layout-to-token mapping</x:v>
@@ -2295,7 +2303,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O22" s="4" t="str">
-        <x:v>document layout-to-token mapping showing a page converted by layout detection, OCR, formula parsing, and coordinate labeling into hierarchical text.</x:v>
+        <x:v>Document structure layout-to-token mapping. The left side shows a fragment of a two-column academic report. The system first uses bounding-box arrays to locate titles, body text, charts, and formula regions. The right side shows how outputs from specialized models such as Nougat and PaddleOCR are post-processed into hierarchical Markdown text and rich text streams with discrete coordinates [xy]. Source: drawn for this book.</x:v>
       </x:c>
       <x:c r="P22" s="4" t="str"/>
       <x:c r="Q22" s="4" t="str">
@@ -2307,7 +2315,7 @@
       <x:c r="S22" s="4" t="str"/>
       <x:c r="T22" s="4" t="str"/>
       <x:c r="U22" s="4" t="str">
-        <x:v>图9-2：文档结构 Layout-to-Token 映射图（Document Structure Layout-to-Token Mapping） —— 左半区展示一份双栏学术报告残页；系统首先通过 Bounding Box 阵列定位标题、正文、图表和公式区域；右半区展示 Nougat、PaddleOCR 等特化模型输出如何经脚本后处理，归并为层级化 Markdown 文本与离散坐标 [xy] 的富文本数据流。来源：本书自绘；Alt text：文档结构 Layout-to-Token 映射图，展示文档页面被版面检测、OCR、公式解析和坐标标注转换为层级文本序列</x:v>
+        <x:v>图9-2：文档结构 Layout-to-Token 映射图（Document Structure Layout-to-Token Mapping） —— 左半区展示一份双栏学术报告残页；系统首先通过 Bounding Box 阵列定位标题、正文、图表和公式区域；右半区展示 Nougat、PaddleOCR 等特化模型输出如何经脚本后处理，归并为层级化 Markdown 文本与离散坐标 [xy] 的富文本数据流。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V22" s="4" t="str">
         <x:v>图9-2：文档结构 Layout-to-Token 映射图</x:v>
@@ -2339,7 +2347,7 @@
         <x:v>10-1</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>Figure 10-1: Distributed audio-video alignment pipeline. Raw mixed videos in the video lake are split into visual and acoustic tracks. Visual-frame extractors and acoustic separators extract features independently before the streams meet in a temporal alignment engine, which produces aligned multimodal JSONL samples with closed timestamp constraints. Source: drawn for this book. Alt text: an audio-video alignment pipeline showing a raw video split into visual, audio, and text tracks and transformed into JSONL by a temporal alignment engine</x:v>
+        <x:v>Figure 10-1: Distributed audio-video alignment pipeline. Raw mixed videos in the video lake are split into visual and acoustic tracks. Visual-frame extractors and acoustic separators extract features independently before the streams meet in a temporal alignment engine, which produces aligned multimodal JSONL samples with closed timestamp constraints. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
         <x:v>Figure 10-1: Distributed audio-video alignment pipeline</x:v>
@@ -2357,7 +2365,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O23" s="4" t="str">
-        <x:v>an audio-video alignment pipeline showing a raw video split into visual, audio, and text tracks and transformed into JSONL by a temporal alignment engine.</x:v>
+        <x:v>Distributed audio-video alignment pipeline. Raw mixed videos in the video lake are split into visual and acoustic tracks. Visual-frame extractors and acoustic separators extract features independently before the streams meet in a temporal alignment engine, which produces aligned multimodal JSONL samples with closed timestamp constraints. Source: drawn for this book.</x:v>
       </x:c>
       <x:c r="P23" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Chapter 10: Video and Audio Data Engineering; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -2371,7 +2379,7 @@
       <x:c r="S23" s="4" t="str"/>
       <x:c r="T23" s="4" t="str"/>
       <x:c r="U23" s="4" t="str">
-        <x:v>图10-1：音视频对齐分布式管线图（Audio-Video Pipeline: Temporal Alignment） —— 左侧原始 Video Lake 中的混合视频被剥离为视觉（Visual Track）和声学（Acoustic Track）双轨并行管线，视觉帧提取器与声学分离器各自提取特征后，最终汇集入跨模态时间对齐引擎（Temporal Alignment Engine），生成带时间戳闭合约束的多模态输入样本（Aligned Multimodal JSONL）。来源：本书自绘；Alt text：音视频对齐分布式管线图，展示原始视频被拆分为视觉轨、音频轨和文本轨，并通过时间对齐引擎生成 JSONL 样本</x:v>
+        <x:v>图10-1：音视频对齐分布式管线图（Audio-Video Pipeline: Temporal Alignment） —— 左侧原始 Video Lake 中的混合视频被剥离为视觉（Visual Track）和声学（Acoustic Track）双轨并行管线，视觉帧提取器与声学分离器各自提取特征后，最终汇集入跨模态时间对齐引擎（Temporal Alignment Engine），生成带时间戳闭合约束的多模态输入样本（Aligned Multimodal JSONL）。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V23" s="4" t="str">
         <x:v>图10-1：音视频对齐分布式管线图</x:v>
@@ -2403,7 +2411,7 @@
         <x:v>10-2</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>Figure 10-2: Adaptive shot-boundary detection and semantic leakage prevention. The upper track extracts aggregated HSV-channel color-space differences, while the lower track extracts optical-flow pixel displacement to capture subtle motion posture. The two tensor differences flow into dual-threshold triage. When the jump score $\Delta$ exceeds the hard-cut threshold, the engine splits the clip and prevents semantic leakage across scenes. Source: drawn for this book. Alt text: adaptive shot-boundary detection showing HSV difference, optical-flow difference, and dual-threshold routing</x:v>
+        <x:v>Figure 10-2: Adaptive shot-boundary detection and semantic leakage prevention. The upper track extracts aggregated HSV-channel color-space differences, while the lower track extracts optical-flow pixel displacement to capture subtle motion posture. The two tensor differences flow into dual-threshold triage. When the jump score $\Delta$ exceeds the hard-cut threshold, the engine splits the clip and prevents semantic leakage across scenes. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
         <x:v>Figure 10-2: Adaptive shot-boundary detection and semantic leakage prevention</x:v>
@@ -2421,7 +2429,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O24" s="4" t="str">
-        <x:v>adaptive shot-boundary detection showing HSV difference, optical-flow difference, and dual-threshold routing.</x:v>
+        <x:v>Adaptive shot-boundary detection and semantic leakage prevention. The upper track extracts aggregated HSV-channel color-space differences, while the lower track extracts optical-flow pixel displacement to capture subtle motion posture. The two tensor differences flow into dual-threshold triage. When the jump score $\Delta$ exceeds the hard-cut threshold, the engine splits the clip and prevents semantic leakage across scenes. Source: drawn for this book.</x:v>
       </x:c>
       <x:c r="P24" s="4" t="str"/>
       <x:c r="Q24" s="4" t="str">
@@ -2433,7 +2441,7 @@
       <x:c r="S24" s="4" t="str"/>
       <x:c r="T24" s="4" t="str"/>
       <x:c r="U24" s="4" t="str">
-        <x:v>图10-2：自适应镜头边界检测与语义防泄漏架构图（Adaptive Shot Boundary Detection &amp; Semantic Leakage Prevention） —— 展示双轨特征侦测逻辑：上层提取 HSV 多通道色彩空间聚合差分，下层提取光流像素位移（Optical Flow）以捕捉细微运动姿态。两种张量差分在右侧汇入“双重阈值路由（Dual-Threshold Triage）”。当突变分值 $\Delta$ 超过硬切阈值（Hard Cut Threshold）时，引擎切分片段，避免场景转换导致视觉切片语义泄漏。来源：本书自绘；Alt text：自适应镜头边界检测图，展示 HSV 差分、光流差分和双阈值路由如何共同判断镜头切分点</x:v>
+        <x:v>图10-2：自适应镜头边界检测与语义防泄漏架构图（Adaptive Shot Boundary Detection &amp; Semantic Leakage Prevention） —— 展示双轨特征侦测逻辑：上层提取 HSV 多通道色彩空间聚合差分，下层提取光流像素位移（Optical Flow）以捕捉细微运动姿态。两种张量差分在右侧汇入“双重阈值路由（Dual-Threshold Triage）”。当突变分值 $\Delta$ 超过硬切阈值（Hard Cut Threshold）时，引擎切分片段，避免场景转换导致视觉切片语义泄漏。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V24" s="4" t="str">
         <x:v>图10-2：自适应镜头边界检测与语义防泄漏架构图</x:v>
@@ -2465,7 +2473,7 @@
         <x:v>10-3</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>Figure 10-3: Large-scale ASR extraction and temporal calibration. Traditional ASR can suffer cumulative temporal drift and semantic errors, such as mishearing I love apples. as maples. WhisperX uses VAD slicing, multi-path acoustic decoding, and a DTW phoneme-level forced-alignment matrix for temporal calibration. The bottom shows word tokens aligned with waveform troughs through vertical dashed lines. Source: drawn for this book. Alt text: ASR extraction and temporal calibration showing traditional ASR drift, WhisperX calibration, and word-level timestamp alignment</x:v>
+        <x:v>Figure 10-3: Large-scale ASR extraction and temporal calibration. Traditional ASR can suffer cumulative temporal drift and semantic errors, such as mishearing I love apples. as maples. WhisperX uses VAD slicing, multi-path acoustic decoding, and a DTW phoneme-level forced-alignment matrix for temporal calibration. The bottom shows word tokens aligned with waveform troughs through vertical dashed lines. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J25" s="4" t="str">
         <x:v>Figure 10-3: Large-scale ASR extraction and temporal calibration</x:v>
@@ -2483,9 +2491,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O25" s="4" t="str">
-        <x:v>ASR extraction and temporal calibration showing traditional ASR drift, WhisperX calibration, and word-level timestamp alignment.</x:v>
-      </x:c>
-      <x:c r="P25" s="4" t="str"/>
+        <x:v>Large-scale ASR extraction and temporal calibration. Traditional ASR can suffer cumulative temporal drift and semantic errors, such as mishearing I love apples. as maples. WhisperX uses VAD slicing, multi-path acoustic decoding, and a DTW phoneme-level forced-alignment matrix for temporal calibration. The bottom shows word tokens aligned with waveform troughs through vertical dashed lines. Source: drawn for this book.</x:v>
+      </x:c>
+      <x:c r="P25" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 10: Video and Audio Data Engineering; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q25" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -2495,7 +2505,7 @@
       <x:c r="S25" s="4" t="str"/>
       <x:c r="T25" s="4" t="str"/>
       <x:c r="U25" s="4" t="str">
-        <x:v>图10-3：大规模 ASR 提取与时间轴动态校准对比图（Large-Scale ASR Extraction &amp; Temporal Calibration） —— 展示传统 ASR 管道在长序列中可能产生累积性时间漂移（Cumulative Temporal Drift）和语义错误（将 I love apples. 误听写为 maples.）；中间展示 WhisperX 通过 VAD 切分、多路声学解码与 DTW（音素级强制对齐）矩阵进行时间校准；底部展示词汇 Token 与音频波谷通过垂直虚线对齐后的输出。来源：本书自绘；Alt text：ASR 提取与时间轴校准对比图，展示传统 ASR 漂移、WhisperX 校准和词级时间戳对齐结果</x:v>
+        <x:v>图10-3：大规模 ASR 提取与时间轴动态校准对比图（Large-Scale ASR Extraction &amp; Temporal Calibration） —— 展示传统 ASR 管道在长序列中可能产生累积性时间漂移（Cumulative Temporal Drift）和语义错误（将 I love apples. 误听写为 maples.）；中间展示 WhisperX 通过 VAD 切分、多路声学解码与 DTW（音素级强制对齐）矩阵进行时间校准；底部展示词汇 Token 与音频波谷通过垂直虚线对齐后的输出。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V25" s="4" t="str">
         <x:v>图10-3：大规模 ASR 提取与时间轴动态校准对比图</x:v>
@@ -2527,7 +2537,7 @@
         <x:v>10-4</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>Figure 10-4: Cross-modal temporal calibration and geometric alignment. The cyan top track is visual key frames, the gray middle track is acoustic features, and the coral bottom track is discrete text tokens. At t=4.2s, the temporal lock binds the visual action "raising a cup," waveform features near the trough, and &lt;start:4.2s "Water cup" text into a unified mixed-token pipeline or JSONL sample. Source: drawn for this book. Alt text: a cross-modal temporal calibration diagram showing visual frames, audio waveform, and text tokens bound by a shared timeline anchor</x:v>
+        <x:v>Figure 10-4: Cross-modal temporal calibration and geometric alignment. The cyan top track is visual key frames, the gray middle track is acoustic features, and the coral bottom track is discrete text tokens. At t=4.2s, the temporal lock binds the visual action "raising a cup," waveform features near the trough, and &lt;start:4.2s "Water cup" text into a unified mixed-token pipeline or JSONL sample. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J26" s="4" t="str">
         <x:v>Figure 10-4: Cross-modal temporal calibration and geometric alignment</x:v>
@@ -2545,9 +2555,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O26" s="4" t="str">
-        <x:v>a cross-modal temporal calibration diagram showing visual frames, audio waveform, and text tokens bound by a shared timeline anchor.</x:v>
-      </x:c>
-      <x:c r="P26" s="4" t="str"/>
+        <x:v>Cross-modal temporal calibration and geometric alignment. The cyan top track is visual key frames, the gray middle track is acoustic features, and the coral bottom track is discrete text tokens. At t=4.2s, the temporal lock binds the visual action "raising a cup," waveform features near the trough, and &lt;start:4.2s "Water cup" text into a unified mixed-token pipeline or JSONL sample. Source: drawn for this book.</x:v>
+      </x:c>
+      <x:c r="P26" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 10: Video and Audio Data Engineering; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q26" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -2557,7 +2569,7 @@
       <x:c r="S26" s="4" t="str"/>
       <x:c r="T26" s="4" t="str"/>
       <x:c r="U26" s="4" t="str">
-        <x:v>图10-4：跨模态时序校准与几何对齐架构图（Cross-Modal Geometric &amp; Temporal Alignment） —— 顶端青色轨道表示视觉关键帧（Visual Modality），中段灰色轨道表示声学特征（Acoustic Modality），底端珊瑚色轨道表示离散文本 Token（Discrete Textual Tokens）。中央时间轴在 t=4.2s 处将“端起水杯的视觉动作”、“波谷处的声学特征”与 &lt;start:4.2s "Water cup" 文本标签绑定，最终生成统一的 Mixed Token Pipeline / JSONL 样本。来源：本书自绘；Alt text：跨模态时序校准图，展示视觉帧、音频波形和文本 Token 如何通过同一时间轴锚点绑定</x:v>
+        <x:v>图10-4：跨模态时序校准与几何对齐架构图（Cross-Modal Geometric &amp; Temporal Alignment） —— 顶端青色轨道表示视觉关键帧（Visual Modality），中段灰色轨道表示声学特征（Acoustic Modality），底端珊瑚色轨道表示离散文本 Token（Discrete Textual Tokens）。中央时间轴在 t=4.2s 处将“端起水杯的视觉动作”、“波谷处的声学特征”与 &lt;start:4.2s "Water cup" 文本标签绑定，最终生成统一的 Mixed Token Pipeline / JSONL 样本。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V26" s="4" t="str">
         <x:v>图10-4：跨模态时序校准与几何对齐架构图</x:v>
@@ -2589,7 +2601,7 @@
         <x:v>11-1</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>Figure 11-1: Three-level cross-modal alignment pyramid. From micro to macro, the bottom is object-level alignment based on BBox, the middle is segment-level alignment based on DTW temporal synchronization, and the top is document-level alignment based on long-context interleaved ordering. Source: drawn for this book. Alt text: a cross-modal alignment pyramid showing object-level, segment-level, and document-level alignment</x:v>
+        <x:v>Figure 11-1: Three-level cross-modal alignment pyramid. From micro to macro, the bottom is object-level alignment based on BBox, the middle is segment-level alignment based on DTW temporal synchronization, and the top is document-level alignment based on long-context interleaved ordering. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J27" s="4" t="str">
         <x:v>Figure 11-1: Three-level cross-modal alignment pyramid</x:v>
@@ -2607,7 +2619,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O27" s="4" t="str">
-        <x:v>a cross-modal alignment pyramid showing object-level, segment-level, and document-level alignment.</x:v>
+        <x:v>Three-level cross-modal alignment pyramid. From micro to macro, the bottom is object-level alignment based on BBox, the middle is segment-level alignment based on DTW temporal synchronization, and the top is document-level alignment based on long-context interleaved ordering. Source: drawn for this book.</x:v>
       </x:c>
       <x:c r="P27" s="4" t="str"/>
       <x:c r="Q27" s="4" t="str">
@@ -2619,7 +2631,7 @@
       <x:c r="S27" s="4" t="str"/>
       <x:c r="T27" s="4" t="str"/>
       <x:c r="U27" s="4" t="str">
-        <x:v>图11-1：跨模态对齐的三级金字塔架构 —— 展现从微观到宏观的三级对齐体系：底层为基于 BBox 的对象级对齐（Object-Level），中层为基于 DTW 时序同步的片段级对齐（Segment-Level），顶层为长上下文交错排序的文档级对齐（Document-Level）。来源：本书自绘；Alt text：跨模态对齐三级金字塔，展示对象级、片段级和文档级对齐之间的层级关系</x:v>
+        <x:v>图11-1：跨模态对齐的三级金字塔架构 —— 展现从微观到宏观的三级对齐体系：底层为基于 BBox 的对象级对齐（Object-Level），中层为基于 DTW 时序同步的片段级对齐（Segment-Level），顶层为长上下文交错排序的文档级对齐（Document-Level）。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V27" s="4" t="str">
         <x:v>图11-1：跨模态对齐的三级金字塔架构</x:v>
@@ -2651,7 +2663,7 @@
         <x:v>11-2</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>Figure 11-2: Multimodal fusion sample design. Independent image, audio, and text pools are assembled into JSONL in the middle. Placeholder grids map them into discrete tokens, and the final result is packed into uniform fusion tensor blocks for downstream pretraining. Source: drawn for this book. Alt text: a multimodal fusion sample design diagram showing image, audio, and text pools mapped through JSONL and placeholders into unified training samples</x:v>
+        <x:v>Figure 11-2: Multimodal fusion sample design. Independent image, audio, and text pools are assembled into JSONL in the middle. Placeholder grids map them into discrete tokens, and the final result is packed into uniform fusion tensor blocks for downstream pretraining. Source: drawn for this book</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
         <x:v>Figure 11-2: Multimodal fusion and hard-negative mining pipeline</x:v>
@@ -2669,7 +2681,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O28" s="4" t="str">
-        <x:v>a multimodal fusion sample design diagram showing image, audio, and text pools mapped through JSONL and placeholders into unified training samples.</x:v>
+        <x:v>Multimodal fusion sample design. Independent image, audio, and text pools are assembled into JSONL in the middle. Placeholder grids map them into discrete tokens, and the final result is packed into uniform fusion tensor blocks for downstream pretraining. Source: drawn for this book.</x:v>
       </x:c>
       <x:c r="P28" s="4" t="str"/>
       <x:c r="Q28" s="4" t="str">
@@ -2681,7 +2693,7 @@
       <x:c r="S28" s="4" t="str"/>
       <x:c r="T28" s="4" t="str"/>
       <x:c r="U28" s="4" t="str">
-        <x:v>图11-2：多模态融合样本设计图 —— 左侧展示独立的图片、音频和文本池，中间展示数据拼装 JSONL 结构，右侧通过占位符技术（Placeholder Grid）映射为离散 Token，最终打包成统一维度的融合张量块供下游模型预训练。来源：本书自绘；Alt text：多模态融合样本设计图，展示图片、音频、文本池如何通过 JSONL 和 Placeholder 映射为统一训练样本</x:v>
+        <x:v>图11-2：多模态融合样本设计图 —— 左侧展示独立的图片、音频和文本池，中间展示数据拼装 JSONL 结构，右侧通过占位符技术（Placeholder Grid）映射为离散 Token，最终打包成统一维度的融合张量块供下游模型预训练。来源：本书自绘</x:v>
       </x:c>
       <x:c r="V28" s="4" t="str">
         <x:v>图11-2：多模态融合与负样本挖掘管线</x:v>
@@ -10417,7 +10429,7 @@
         <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
       </x:c>
       <x:c r="G152" s="4" t="n">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H152" s="4" t="str">
         <x:v>45-1</x:v>
@@ -10479,7 +10491,7 @@
         <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
       </x:c>
       <x:c r="G153" s="4" t="n">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H153" s="4" t="str">
         <x:v>45-2</x:v>
@@ -10541,7 +10553,7 @@
         <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
       </x:c>
       <x:c r="G154" s="4" t="n">
-        <x:v>233</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H154" s="4" t="str">
         <x:v>45-3</x:v>
@@ -10603,7 +10615,7 @@
         <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
       </x:c>
       <x:c r="G155" s="4" t="n">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H155" s="4" t="str">
         <x:v>46-1</x:v>
@@ -10665,7 +10677,7 @@
         <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
       </x:c>
       <x:c r="G156" s="4" t="n">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H156" s="4" t="str">
         <x:v>46-2</x:v>
@@ -10727,7 +10739,7 @@
         <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
       </x:c>
       <x:c r="G157" s="4" t="n">
-        <x:v>219</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H157" s="4" t="str">
         <x:v>46-3</x:v>
@@ -11695,7 +11707,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O172" s="4" t="str">
-        <x:v>Data Retention Funnel. --- Figure P01-8: Data Retention Funnel The final retention funnel obtained by this project is as follows:.</x:v>
+        <x:v>Data Retention Funnel. --- Figure P01-8: Data Retention Funnel.</x:v>
       </x:c>
       <x:c r="P172" s="4" t="str"/>
       <x:c r="Q172" s="4" t="str">
@@ -11819,7 +11831,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O174" s="4" t="str">
-        <x:v>Project Validation Loop. Figure P01-10: Project Validation Loop If a data engineering project has only output files and no inspection mechanism, it is actually difficult to say whether it is truly correct.</x:v>
+        <x:v>Project Validation Loop. Figure P01-10: Project Validation Loop.</x:v>
       </x:c>
       <x:c r="P174" s="4" t="str"/>
       <x:c r="Q174" s="4" t="str">
@@ -17693,7 +17705,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O268" s="4" t="str">
-        <x:v>Preflight Check Process. Because it reflects a mature engineering practice: Not "run first, then observe," but "confirm that minimum conditions are met first, then proceed to higher-risk processing and exercise stages." Figure P09-10: Preflight Check Process --- Many case studies describe only the success path, not the failure path.</x:v>
+        <x:v>Preflight Check Process. Because it reflects a mature engineering practice: Not "run first, then observe," but "confirm that minimum conditions are met first, then proceed to higher-risk processing and exercise stages." Figure P09-10: Preflight Check Process.</x:v>
       </x:c>
       <x:c r="P268" s="4" t="str"/>
       <x:c r="Q268" s="4" t="str">

--- a/publishing/accessibility/springer_alt_text_inventory.xlsx
+++ b/publishing/accessibility/springer_alt_text_inventory.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R96cc8c0e27bf4285"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="Rcb1eac0eb3044b1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R0a18deb6ffb14752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1fcb29f994d34ff4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R858b4d3cac164c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R5ef60f777a8e461f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -323,7 +323,7 @@
         <x:v>Generated at UTC</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>46195.21366738426</x:v>
+        <x:v>46195.457691574076</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -18843,35 +18843,33 @@
         <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
       </x:c>
       <x:c r="G287" s="4" t="n">
-        <x:v>150</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H287" s="4" t="str">
         <x:v>P15-1</x:v>
       </x:c>
       <x:c r="I287" s="4" t="str">
-        <x:v>Figure P15-1: Layered architecture for the DataAgent enterprise semantic BI assistant</x:v>
+        <x:v>Figure P15-1: Engineering chain of the DataAgent semantic BI assistant</x:v>
       </x:c>
       <x:c r="J287" s="4" t="str">
-        <x:v>Layered architecture for a DataAgent enterprise semantic BI assistant</x:v>
+        <x:v>DataAgent semantic BI assistant engineering chain</x:v>
       </x:c>
       <x:c r="K287" s="4" t="str">
-        <x:v>docs/images/part14/p15_dataagent_semantic_bi_layered_architecture_en.png</x:v>
+        <x:v>docs/images/part14/p15_dataagent_engineering_chain_en.png</x:v>
       </x:c>
       <x:c r="L287" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M287" s="4" t="str">
-        <x:v>1600x1104</x:v>
+        <x:v>1536x1024</x:v>
       </x:c>
       <x:c r="N287" s="4" t="str">
         <x:v>png</x:v>
       </x:c>
       <x:c r="O287" s="4" t="str">
-        <x:v>Layered architecture for the DataAgent enterprise semantic BI assistant.</x:v>
-      </x:c>
-      <x:c r="P287" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 15: Building an Enterprise Semantic BI Assistant with DataAgent; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Engineering chain of the DataAgent semantic BI assistant.</x:v>
+      </x:c>
+      <x:c r="P287" s="4" t="str"/>
       <x:c r="Q287" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -18881,10 +18879,10 @@
       <x:c r="S287" s="4" t="str"/>
       <x:c r="T287" s="4" t="str"/>
       <x:c r="U287" s="4" t="str">
-        <x:v>Figure P15-1：DataAgent 企业语义问数助手分层架构</x:v>
+        <x:v>Figure P15-1：DataAgent 语义问数助手工程链路</x:v>
       </x:c>
       <x:c r="V287" s="4" t="str">
-        <x:v>DataAgent 企业语义问数助手分层架构</x:v>
+        <x:v>DataAgent 语义问数助手工程链路</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -18907,31 +18905,31 @@
         <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
       </x:c>
       <x:c r="G288" s="4" t="n">
-        <x:v>156</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H288" s="4" t="str">
         <x:v>P15-2</x:v>
       </x:c>
       <x:c r="I288" s="4" t="str">
-        <x:v>Figure P15-2: Overall architecture of the DataAgent repository</x:v>
+        <x:v>Figure P15-2: DataGallery ecosystem architecture around DataAgent</x:v>
       </x:c>
       <x:c r="J288" s="4" t="str">
-        <x:v>DataAgent overall architecture</x:v>
+        <x:v>DataGallery ecosystem architecture around DataAgent, Semantic Service, Data Studio, Data Ops, and foundation infrastructure</x:v>
       </x:c>
       <x:c r="K288" s="4" t="str">
-        <x:v>docs/images/part14/p15_dataagent_agent_excalidraw_en.png</x:v>
+        <x:v>docs/images/part14/p15_datagallery_architecture_vector.svg</x:v>
       </x:c>
       <x:c r="L288" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M288" s="4" t="str">
-        <x:v>1657x1399</x:v>
+        <x:v>1536x1024</x:v>
       </x:c>
       <x:c r="N288" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O288" s="4" t="str">
-        <x:v>Overall architecture of the DataAgent repository.</x:v>
+        <x:v>DataGallery ecosystem architecture around DataAgent.</x:v>
       </x:c>
       <x:c r="P288" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Project 15: Building an Enterprise Semantic BI Assistant with DataAgent; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -18945,10 +18943,10 @@
       <x:c r="S288" s="4" t="str"/>
       <x:c r="T288" s="4" t="str"/>
       <x:c r="U288" s="4" t="str">
-        <x:v>Figure P15-2：DataAgent 仓库整体架构图</x:v>
+        <x:v>Figure P15-2：围绕 DataAgent 展开的 DataGallery 生态架构</x:v>
       </x:c>
       <x:c r="V288" s="4" t="str">
-        <x:v>DataAgent 整体架构图</x:v>
+        <x:v>围绕 DataAgent、Semantic Service、Data Studio、Data Ops 与基础设施展开的 DataGallery 生态架构</x:v>
       </x:c>
     </x:row>
     <x:row r="289">
@@ -18971,7 +18969,7 @@
         <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
       </x:c>
       <x:c r="G289" s="4" t="n">
-        <x:v>586</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="H289" s="4" t="str">
         <x:v>P15-3</x:v>
